--- a/data/trans_orig/P1803_2016_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1803_2016_2023-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57692</t>
+          <t>55982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>53892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>88044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>712612</t>
+          <t>714337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>734415</t>
+          <t>735620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>936968</t>
+          <t>938678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>964574</t>
+          <t>965257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1661216</t>
+          <t>1660963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1695364</t>
+          <t>1695115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110409</t>
+          <t>108586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85818</t>
+          <t>85528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127799</t>
+          <t>126006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167439</t>
+          <t>167760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220615</t>
+          <t>225133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1965976</t>
+          <t>1967799</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2004691</t>
+          <t>2006350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1860501</t>
+          <t>1862294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1902482</t>
+          <t>1902772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3844070</t>
+          <t>3839552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3897246</t>
+          <t>3896925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26187</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52350</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>36288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64123</t>
+          <t>62998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>68920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107906</t>
+          <t>105844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494536</t>
+          <t>495685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520699</t>
+          <t>521408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>485017</t>
+          <t>486142</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513436</t>
+          <t>512852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>988121</t>
+          <t>990183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026480</t>
+          <t>1027107</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130268</t>
+          <t>132142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181117</t>
+          <t>182616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166206</t>
+          <t>169654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222342</t>
+          <t>224336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>312490</t>
+          <t>313388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388320</t>
+          <t>387783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3196501</t>
+          <t>3195002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3247350</t>
+          <t>3245476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3309758</t>
+          <t>3307764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3365894</t>
+          <t>3362446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6521398</t>
+          <t>6521935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6597228</t>
+          <t>6596330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51081</t>
+          <t>54874</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>45982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62042</t>
+          <t>66530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>72851</t>
+          <t>78221</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60188</t>
+          <t>65229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86582</t>
+          <t>92710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>493168</t>
+          <t>555181</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>483910</t>
+          <t>544960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500382</t>
+          <t>563340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>703861</t>
+          <t>766568</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>692900</t>
+          <t>754912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>712573</t>
+          <t>775460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1197030</t>
+          <t>1321750</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1183299</t>
+          <t>1307261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1209693</t>
+          <t>1334742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>410051</t>
+          <t>171653</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176676</t>
+          <t>145604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1043281</t>
+          <t>201670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>188755</t>
+          <t>204416</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139217</t>
+          <t>184020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221212</t>
+          <t>231119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>598807</t>
+          <t>376068</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>357388</t>
+          <t>334117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1364430</t>
+          <t>412762</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1880276</t>
+          <t>2058913</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1247046</t>
+          <t>2028896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2113651</t>
+          <t>2084962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2048390</t>
+          <t>1966291</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2015933</t>
+          <t>1939588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2097928</t>
+          <t>1986687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3928665</t>
+          <t>4025206</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3163042</t>
+          <t>3988512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4170084</t>
+          <t>4067157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>82686</t>
+          <t>86996</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66520</t>
+          <t>69286</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104473</t>
+          <t>108886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>110126</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89356</t>
+          <t>94309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123892</t>
+          <t>129168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>187515</t>
+          <t>197121</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163572</t>
+          <t>169985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215352</t>
+          <t>224131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>563937</t>
+          <t>624591</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542150</t>
+          <t>602701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>580103</t>
+          <t>642301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>555633</t>
+          <t>624751</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>536571</t>
+          <t>605709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>571107</t>
+          <t>640568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1119571</t>
+          <t>1249343</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1091734</t>
+          <t>1222333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1143514</t>
+          <t>1276479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276909</t>
+          <t>246681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1168231</t>
+          <t>317741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>369415</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>282260</t>
+          <t>337907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386596</t>
+          <t>402070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>859173</t>
+          <t>651411</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>617953</t>
+          <t>602992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1656994</t>
+          <t>698679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2937382</t>
+          <t>3238687</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2283658</t>
+          <t>3202942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3174980</t>
+          <t>3274002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3307884</t>
+          <t>3357611</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3265954</t>
+          <t>3324956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3370290</t>
+          <t>3389119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6245266</t>
+          <t>6596298</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5447445</t>
+          <t>6549030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6486486</t>
+          <t>6644717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
